--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ConditionDiseaseCodeReceipt_CS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/masterB-disease</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-receipt-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeReceipt_VS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ConditionDiseaseCodeReceipt_VS</t>
+    <t>JP_Disease_Claim_VS</t>
   </si>
   <si>
     <t>Title</t>
